--- a/stories/arbres/TREE-DIF-041.xlsx
+++ b/stories/arbres/TREE-DIF-041.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Kenzo est avec papa, dans le train avec papa. Kenzo a envie de jouer. papa est là, tout près. On va apprendre : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo écoute papa. Kenzo entend les mots : proposer, accepter plusieurs réponses.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Kenzo va vers la cuisine. Une feuille tombe. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Kenzo se souvient : proposer, accepter plusieurs réponses. Voici le geste : inviter ; accepter. On se tait une seconde. papa dit : je suis là. On reste ensemble.</t>
+          <t>Kenzo va vers la cuisine. Une feuille tombe. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Kenzo se souvient : proposer, accepter plusieurs réponses. Voici le geste : inviter ; accepter. On se tait une seconde. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,12 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo va vers la cuisine. Une feuille tombe. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Kenzo se souvient : proposer, accepter plusieurs réponses. Voici le geste : inviter ; accepter. On se tait une seconde.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1862,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Inviter sans forcer.</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2035,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : inviter ; accepter. Kenzo respire. Kenzo retient : proposer, accepter plusieurs réponses. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2183,6 +2226,11 @@
         <v>12</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2345,6 +2393,11 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi les cubes. Un vélo passe au loin. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : inviter ; accepter. Kenzo répète tout bas : proposer, accepter plusieurs réponses. On dit merci. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2531,6 +2584,11 @@
         <v>12</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2693,6 +2751,11 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le matin. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de la cuisine, les cubes et le matin. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2918,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3085,11 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint après la sieste. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3252,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3419,11 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le soir. La couverture est douce. On range un objet. Cette fin-là est celle de la cuisine, les cubes et le soir. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3586,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3753,11 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi le livre. La lumière est claire. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : inviter ; accepter. Kenzo répète tout bas : proposer, accepter plusieurs réponses. On souffle doucement. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3851,6 +3944,11 @@
         <v>12</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4013,6 +4111,11 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le matin. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de la cuisine, le livre et le matin. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4175,6 +4278,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4337,6 +4445,11 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint après la sieste. La couverture est douce. On se tient la main. Cette fin-là est celle de la cuisine, le livre et après la sieste. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4499,6 +4612,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4661,6 +4779,11 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le soir. On entend un oiseau. On range un objet. Cette fin-là est celle de la cuisine, le livre et le soir. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4823,6 +4946,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4985,6 +5113,11 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi la dînette. Il y a des miettes sur la table. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : inviter ; accepter. Kenzo répète tout bas : proposer, accepter plusieurs réponses. On écoute jusqu'au bout. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5171,6 +5304,11 @@
         <v>12</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5333,6 +5471,11 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le matin. La couverture est douce. On se tait une seconde. Cette fin-là est celle de la cuisine, la dînette et le matin. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5495,6 +5638,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5657,6 +5805,11 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint après la sieste. On entend un oiseau. On se tient la main. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5819,6 +5972,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5981,6 +6139,11 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le soir. Ça sent le pain chaud. On range un objet. Cette fin-là est celle de la cuisine, la dînette et le soir. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6143,6 +6306,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6167,7 +6335,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Kenzo va vers le jardin. L'eau coule, tout petit bruit. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Kenzo se souvient : proposer, accepter plusieurs réponses. Voici le geste : inviter ; accepter. On se tient la main. papa dit : je suis là. On reste ensemble.</t>
+          <t>Kenzo va vers le jardin. L'eau coule, tout petit bruit. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Kenzo se souvient : proposer, accepter plusieurs réponses. Voici le geste : inviter ; accepter. On se tient la main. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6305,6 +6473,12 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo va vers le jardin. L'eau coule, tout petit bruit. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Kenzo se souvient : proposer, accepter plusieurs réponses. Voici le geste : inviter ; accepter. On se tient la main.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6485,6 +6659,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Inviter sans forcer.</t>
         </is>
       </c>
     </row>
@@ -6653,6 +6832,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : inviter ; accepter. Kenzo respire. Kenzo retient : proposer, accepter plusieurs réponses. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6839,6 +7023,11 @@
         <v>12</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7001,6 +7190,11 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi les cubes. Un chat miaule une fois. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : inviter ; accepter. Kenzo répète tout bas : proposer, accepter plusieurs réponses. On dit merci. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7187,6 +7381,11 @@
         <v>12</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7349,6 +7548,11 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le matin. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de le jardin, les cubes et le matin. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7511,6 +7715,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7673,6 +7882,11 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint après la sieste. La couverture est douce. On range un objet. Cette fin-là est celle de le jardin, les cubes et après la sieste. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7835,6 +8049,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7997,6 +8216,11 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le soir. On entend un oiseau. On dit merci. Cette fin-là est celle de le jardin, les cubes et le soir. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8159,6 +8383,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8321,6 +8550,11 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi le livre. Les chaussures font toc toc. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : inviter ; accepter. Kenzo répète tout bas : proposer, accepter plusieurs réponses. On souffle doucement. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8507,6 +8741,11 @@
         <v>12</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8669,6 +8908,11 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le matin. La couverture est douce. On se tient la main. Cette fin-là est celle de le jardin, le livre et le matin. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8831,6 +9075,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8993,6 +9242,11 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint après la sieste. On entend un oiseau. On range un objet. Cette fin-là est celle de le jardin, le livre et après la sieste. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9155,6 +9409,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9317,6 +9576,11 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le soir. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de le jardin, le livre et le soir. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9479,6 +9743,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9641,6 +9910,11 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi la dînette. La couverture est douce. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : inviter ; accepter. Kenzo répète tout bas : proposer, accepter plusieurs réponses. On écoute jusqu'au bout. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9827,6 +10101,11 @@
         <v>12</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9989,6 +10268,11 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le matin. On entend un oiseau. On se tient la main. Cette fin-là est celle de le jardin, la dînette et le matin. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10151,6 +10435,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10313,6 +10602,11 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint après la sieste. Ça sent le pain chaud. On range un objet. Cette fin-là est celle de le jardin, la dînette et après la sieste. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10475,6 +10769,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10637,6 +10936,11 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le soir. Le vent est doux. On dit merci. Cette fin-là est celle de le jardin, la dînette et le soir. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10799,6 +11103,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10823,7 +11132,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Kenzo va vers la chambre. Un vélo passe au loin. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Kenzo se souvient : proposer, accepter plusieurs réponses. Voici le geste : inviter ; accepter. On range un objet. papa dit : je suis là. On reste ensemble.</t>
+          <t>Kenzo va vers la chambre. Un vélo passe au loin. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Kenzo se souvient : proposer, accepter plusieurs réponses. Voici le geste : inviter ; accepter. On range un objet. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10961,6 +11270,12 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo va vers la chambre. Un vélo passe au loin. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Kenzo se souvient : proposer, accepter plusieurs réponses. Voici le geste : inviter ; accepter. On range un objet.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11141,6 +11456,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Inviter sans forcer.</t>
         </is>
       </c>
     </row>
@@ -11309,6 +11629,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : inviter ; accepter. Kenzo respire. Kenzo retient : proposer, accepter plusieurs réponses. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11495,6 +11820,11 @@
         <v>12</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11657,6 +11987,11 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi les cubes. On entend un oiseau. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : inviter ; accepter. Kenzo répète tout bas : proposer, accepter plusieurs réponses. On dit merci. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11843,6 +12178,11 @@
         <v>12</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12005,6 +12345,11 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le matin. La couverture est douce. On range un objet. Cette fin-là est celle de la chambre, les cubes et le matin. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12167,6 +12512,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12329,6 +12679,11 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint après la sieste. On entend un oiseau. On dit merci. Cette fin-là est celle de la chambre, les cubes et après la sieste. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12491,6 +12846,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12653,6 +13013,11 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le soir. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de la chambre, les cubes et le soir. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12815,6 +13180,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12977,6 +13347,11 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi le livre. Ça sent le pain chaud. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : inviter ; accepter. Kenzo répète tout bas : proposer, accepter plusieurs réponses. On souffle doucement. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13163,6 +13538,11 @@
         <v>12</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13325,6 +13705,11 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le matin. On entend un oiseau. On range un objet. Cette fin-là est celle de la chambre, le livre et le matin. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13487,6 +13872,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13649,6 +14039,11 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint après la sieste. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de la chambre, le livre et après la sieste. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13811,6 +14206,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13973,6 +14373,11 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le soir. Le vent est doux. On souffle doucement. Cette fin-là est celle de la chambre, le livre et le soir. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14135,6 +14540,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14297,6 +14707,11 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi la dînette. Le vent est doux. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : inviter ; accepter. Kenzo répète tout bas : proposer, accepter plusieurs réponses. On écoute jusqu'au bout. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14483,6 +14898,11 @@
         <v>12</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14645,6 +15065,11 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le matin. Ça sent le pain chaud. On range un objet. Cette fin-là est celle de la chambre, la dînette et le matin. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14807,6 +15232,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14969,6 +15399,11 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint après la sieste. Le vent est doux. On dit merci. Cette fin-là est celle de la chambre, la dînette et après la sieste. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15131,6 +15566,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15293,6 +15733,11 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le soir. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de la chambre, la dînette et le soir. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15455,6 +15900,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15473,7 +15923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15490,6 +15940,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-DIF-041.xlsx
+++ b/stories/arbres/TREE-DIF-041.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Kenzo est avec papa, dans le train avec papa. Kenzo a envie de jouer. papa est là, tout près. On va apprendre : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo écoute papa. Kenzo entend les mots : proposer, accepter plusieurs réponses.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1869,6 +1877,7 @@
           <t>narrateur|Que fait-on ? Inviter sans forcer.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2040,6 +2049,7 @@
           <t>narrateur|Oui. Voici le geste : inviter ; accepter. Kenzo respire. Kenzo retient : proposer, accepter plusieurs réponses. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2231,6 +2241,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2398,6 +2409,7 @@
           <t>narrateur|Kenzo a choisi les cubes. Un vélo passe au loin. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : inviter ; accepter. Kenzo répète tout bas : proposer, accepter plusieurs réponses. On dit merci. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2589,6 +2601,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2756,6 +2769,7 @@
           <t>narrateur|Kenzo rejoint le matin. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de la cuisine, les cubes et le matin. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2923,6 +2937,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3090,6 +3105,7 @@
           <t>narrateur|Kenzo rejoint après la sieste. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3257,6 +3273,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3424,6 +3441,7 @@
           <t>narrateur|Kenzo rejoint le soir. La couverture est douce. On range un objet. Cette fin-là est celle de la cuisine, les cubes et le soir. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3591,6 +3609,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3758,6 +3777,7 @@
           <t>narrateur|Kenzo a choisi le livre. La lumière est claire. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : inviter ; accepter. Kenzo répète tout bas : proposer, accepter plusieurs réponses. On souffle doucement. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3949,6 +3969,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4116,6 +4137,7 @@
           <t>narrateur|Kenzo rejoint le matin. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de la cuisine, le livre et le matin. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4283,6 +4305,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4450,6 +4473,7 @@
           <t>narrateur|Kenzo rejoint après la sieste. La couverture est douce. On se tient la main. Cette fin-là est celle de la cuisine, le livre et après la sieste. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4617,6 +4641,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4784,6 +4809,7 @@
           <t>narrateur|Kenzo rejoint le soir. On entend un oiseau. On range un objet. Cette fin-là est celle de la cuisine, le livre et le soir. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4951,6 +4977,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5118,6 +5145,7 @@
           <t>narrateur|Kenzo a choisi la dînette. Il y a des miettes sur la table. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : inviter ; accepter. Kenzo répète tout bas : proposer, accepter plusieurs réponses. On écoute jusqu'au bout. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5309,6 +5337,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5476,6 +5505,7 @@
           <t>narrateur|Kenzo rejoint le matin. La couverture est douce. On se tait une seconde. Cette fin-là est celle de la cuisine, la dînette et le matin. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5643,6 +5673,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5810,6 +5841,7 @@
           <t>narrateur|Kenzo rejoint après la sieste. On entend un oiseau. On se tient la main. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5977,6 +6009,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6144,6 +6177,7 @@
           <t>narrateur|Kenzo rejoint le soir. Ça sent le pain chaud. On range un objet. Cette fin-là est celle de la cuisine, la dînette et le soir. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6311,6 +6345,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6479,6 +6514,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6666,6 +6702,7 @@
           <t>narrateur|Que fait-on ? Inviter sans forcer.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6837,6 +6874,7 @@
           <t>narrateur|Oui. Voici le geste : inviter ; accepter. Kenzo respire. Kenzo retient : proposer, accepter plusieurs réponses. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7028,6 +7066,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7195,6 +7234,7 @@
           <t>narrateur|Kenzo a choisi les cubes. Un chat miaule une fois. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : inviter ; accepter. Kenzo répète tout bas : proposer, accepter plusieurs réponses. On dit merci. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7386,6 +7426,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7553,6 +7594,7 @@
           <t>narrateur|Kenzo rejoint le matin. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de le jardin, les cubes et le matin. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7720,6 +7762,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7887,6 +7930,7 @@
           <t>narrateur|Kenzo rejoint après la sieste. La couverture est douce. On range un objet. Cette fin-là est celle de le jardin, les cubes et après la sieste. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8054,6 +8098,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8221,6 +8266,7 @@
           <t>narrateur|Kenzo rejoint le soir. On entend un oiseau. On dit merci. Cette fin-là est celle de le jardin, les cubes et le soir. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8388,6 +8434,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8555,6 +8602,7 @@
           <t>narrateur|Kenzo a choisi le livre. Les chaussures font toc toc. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : inviter ; accepter. Kenzo répète tout bas : proposer, accepter plusieurs réponses. On souffle doucement. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8746,6 +8794,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8913,6 +8962,7 @@
           <t>narrateur|Kenzo rejoint le matin. La couverture est douce. On se tient la main. Cette fin-là est celle de le jardin, le livre et le matin. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9080,6 +9130,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9247,6 +9298,7 @@
           <t>narrateur|Kenzo rejoint après la sieste. On entend un oiseau. On range un objet. Cette fin-là est celle de le jardin, le livre et après la sieste. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9414,6 +9466,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9581,6 +9634,7 @@
           <t>narrateur|Kenzo rejoint le soir. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de le jardin, le livre et le soir. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9748,6 +9802,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9915,6 +9970,7 @@
           <t>narrateur|Kenzo a choisi la dînette. La couverture est douce. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : inviter ; accepter. Kenzo répète tout bas : proposer, accepter plusieurs réponses. On écoute jusqu'au bout. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10106,6 +10162,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10273,6 +10330,7 @@
           <t>narrateur|Kenzo rejoint le matin. On entend un oiseau. On se tient la main. Cette fin-là est celle de le jardin, la dînette et le matin. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10440,6 +10498,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10607,6 +10666,7 @@
           <t>narrateur|Kenzo rejoint après la sieste. Ça sent le pain chaud. On range un objet. Cette fin-là est celle de le jardin, la dînette et après la sieste. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10774,6 +10834,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10941,6 +11002,7 @@
           <t>narrateur|Kenzo rejoint le soir. Le vent est doux. On dit merci. Cette fin-là est celle de le jardin, la dînette et le soir. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11108,6 +11170,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11276,6 +11339,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11463,6 +11527,7 @@
           <t>narrateur|Que fait-on ? Inviter sans forcer.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11634,6 +11699,7 @@
           <t>narrateur|Oui. Voici le geste : inviter ; accepter. Kenzo respire. Kenzo retient : proposer, accepter plusieurs réponses. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11825,6 +11891,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11992,6 +12059,7 @@
           <t>narrateur|Kenzo a choisi les cubes. On entend un oiseau. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : inviter ; accepter. Kenzo répète tout bas : proposer, accepter plusieurs réponses. On dit merci. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12183,6 +12251,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12350,6 +12419,7 @@
           <t>narrateur|Kenzo rejoint le matin. La couverture est douce. On range un objet. Cette fin-là est celle de la chambre, les cubes et le matin. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12517,6 +12587,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12684,6 +12755,7 @@
           <t>narrateur|Kenzo rejoint après la sieste. On entend un oiseau. On dit merci. Cette fin-là est celle de la chambre, les cubes et après la sieste. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12851,6 +12923,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13018,6 +13091,7 @@
           <t>narrateur|Kenzo rejoint le soir. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de la chambre, les cubes et le soir. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13185,6 +13259,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13352,6 +13427,7 @@
           <t>narrateur|Kenzo a choisi le livre. Ça sent le pain chaud. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : inviter ; accepter. Kenzo répète tout bas : proposer, accepter plusieurs réponses. On souffle doucement. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13543,6 +13619,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13710,6 +13787,7 @@
           <t>narrateur|Kenzo rejoint le matin. On entend un oiseau. On range un objet. Cette fin-là est celle de la chambre, le livre et le matin. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13877,6 +13955,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14044,6 +14123,7 @@
           <t>narrateur|Kenzo rejoint après la sieste. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de la chambre, le livre et après la sieste. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14211,6 +14291,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14378,6 +14459,7 @@
           <t>narrateur|Kenzo rejoint le soir. Le vent est doux. On souffle doucement. Cette fin-là est celle de la chambre, le livre et le soir. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14545,6 +14627,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14712,6 +14795,7 @@
           <t>narrateur|Kenzo a choisi la dînette. Le vent est doux. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : inviter ; accepter. Kenzo répète tout bas : proposer, accepter plusieurs réponses. On écoute jusqu'au bout. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14903,6 +14987,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15070,6 +15155,7 @@
           <t>narrateur|Kenzo rejoint le matin. Ça sent le pain chaud. On range un objet. Cette fin-là est celle de la chambre, la dînette et le matin. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15237,6 +15323,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15404,6 +15491,7 @@
           <t>narrateur|Kenzo rejoint après la sieste. Le vent est doux. On dit merci. Cette fin-là est celle de la chambre, la dînette et après la sieste. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15571,6 +15659,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15738,6 +15827,7 @@
           <t>narrateur|Kenzo rejoint le soir. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de la chambre, la dînette et le soir. Kenzo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Kenzo a entendu : proposer, accepter plusieurs réponses. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15905,6 +15995,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15923,7 +16014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15947,6 +16038,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15961,7 +16066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16148,6 +16253,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-DIF-041.xlsx
+++ b/stories/arbres/TREE-DIF-041.xlsx
@@ -1197,17 +1197,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La gare du village sent le café. Les pierres du quai brillent, mouillées. Un train long attend, silencieux. Ça sent le sel, mêlé au café. Une flaque tremble entre deux pierres. Un sac de papier laisse filer de la chaleur. Le pain est tiède, Amir. Les billets sont dans ma poche. Un goéland passe, trop haut pour le quai. La mer est derrière, pas loin. Nina est dans le wagon. Je veux lui montrer la mer. En ce moment, Amir monte la marche. Le marchepied est haut. Merci, tu tiens le sac bien. On va jusqu'à la mer. Le papier du pain craque, chaud.</t>
+          <t>La gare du village sent le café. Les pierres du quai brillent, mouillées. Un train long attend, silencieux. Ça sent le sel, mêlé au café. Une flaque tremble entre deux pierres. Un sac de papier laisse filer de la chaleur. Le pain tiède est à toi, Amir. Les billets sont dans ma poche. Un goéland passe, trop haut pour le quai. La mer est derrière, pas loin. Nina est dans le wagon. Je veux lui montrer la mer. En ce moment, Amir monte la marche. Le marchepied est haut. Merci, tu tiens le sac bien. On va jusqu'à la mer. Le papier du pain craque, chaud.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La gare du village sent le café. Les pierres du quai brillent, mouillées. Un train long attend, silencieux. Ça sent le sel, mêlé au café. Une flaque tremble entre deux pierres. Un sac de papier laisse filer de la chaleur. Le pain est tiède, Amir. Les billets sont dans ma poche. Un goéland passe, trop haut pour le quai. La mer est derrière, pas loin. Nina est dans le wagon. Je veux lui montrer la mer. En ce moment, Amir monte la marche. Le marchepied est haut. Merci, tu tiens le sac bien. On va jusqu'à la mer. Le papier du pain craque, chaud.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La gare du village sent le café. Les pierres du quai brillent, mouillées. Un train long attend, silencieux. Ça sent le sel, mêlé au café. Une flaque tremble entre deux pierres. Un sac de papier laisse filer de la chaleur. Le &lt;emphasis level="moderate"&gt;pain tiède&lt;/emphasis&gt; est à toi, Amir. Les billets sont dans ma poche. Un goéland passe, trop haut pour le quai. La mer est derrière, pas loin. Nina est dans le wagon. Je veux lui montrer la mer. En ce moment, Amir monte la marche. Le marchepied est haut. Merci, tu tiens le sac bien. On va jusqu'à la mer. Le papier du pain craque, chaud.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>La gare du village sent le café. Les pierres du quai brillent, mouillées. Un train long attend, silencieux. Ça sent le sel, mêlé au café. Une flaque tremble entre deux pierres. Un sac de papier laisse filer de la chaleur. Le pain est tiède, Amir. Les billets sont dans ma poche. Un goéland passe, trop haut pour le quai. La mer est derrière, pas loin. Nina est dans le wagon. Je veux lui montrer la mer. En ce moment, Amir monte la marche. Le marchepied est haut. Merci, tu tiens le sac bien. On va jusqu'à la mer. Le papier du pain craque, chaud. [pause]</t>
+          <t>La gare du village sent le café. Les pierres du quai brillent, mouillées. Un train long attend, silencieux. Ça sent le sel, mêlé au café. Une flaque tremble entre deux pierres. Un sac de papier laisse filer de la chaleur. Le &lt;emphasis&gt;pain tiède&lt;/emphasis&gt; est à toi, Amir. Les billets sont dans ma poche. Un goéland passe, trop haut pour le quai. La mer est derrière, pas loin. Nina est dans le wagon. Je veux lui montrer la mer. En ce moment, Amir monte la marche. Le marchepied est haut. Merci, tu tiens le sac bien. On va jusqu'à la mer. Le papier du pain craque, chaud. [pause]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1347,7 +1347,7 @@
 narrateur|Ça sent le sel, mêlé au café.
 narrateur|Une flaque tremble entre deux pierres.
 narrateur|Un sac de papier laisse filer de la chaleur.
-maman|Le pain est tiède, Amir.
+maman|Le pain tiède est à toi, Amir.
 papa|Les billets sont dans ma poche.
 narrateur|Un goéland passe, trop haut pour le quai.
 enfant-m|La mer est derrière, pas loin.
@@ -6487,17 +6487,17 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>On regarde plus tard, alors ? Oui, plus tard. D'accord. La vitre garde sa place, sans lui. Nina serre l'oreille, toujours. Garde la mer pour moi. Elle t'attend. Tu as proposé une autre heure. Elle a dit oui, pour plus tard. Amir laisse un siège vide, à dessein.</t>
+          <t>On regarde plus tard, alors ? Oui, plus tard. D'accord. La vitre garde sa place, sans lui. Nina serre l'oreille, sans bouger. Garde la mer pour moi. Elle t'attend. Tu as proposé une autre heure. Elle a dit oui, pour plus tard. Amir laisse un siège vide, à dessein.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;On regarde &lt;emphasis level="moderate"&gt;plus tard&lt;/emphasis&gt;, alors ? Oui, plus tard. D'accord. La vitre garde sa place, sans lui. Nina serre l'oreille, toujours. Garde la mer pour moi. Elle t'attend. Tu as proposé une autre heure. Elle a dit oui, pour plus tard. Amir laisse un siège vide, à dessein.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;On regarde &lt;emphasis level="moderate"&gt;plus tard&lt;/emphasis&gt;, alors ? Oui, plus tard. D'accord. La vitre garde sa place, sans lui. Nina serre l'oreille, sans bouger. Garde la mer pour moi. Elle t'attend. Tu as proposé une autre heure. Elle a dit oui, pour plus tard. Amir laisse un siège vide, à dessein.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>On regarde &lt;emphasis&gt;plus tard&lt;/emphasis&gt;, alors ? Oui, plus tard. D'accord. La vitre garde sa place, sans lui. Nina serre l'oreille, toujours. Garde la mer pour moi. Elle t'attend. Tu as proposé une autre heure. Elle a dit oui, pour plus tard. Amir laisse un siège vide, à dessein. [pause]</t>
+          <t>On regarde &lt;emphasis&gt;plus tard&lt;/emphasis&gt;, alors ? Oui, plus tard. D'accord. La vitre garde sa place, sans lui. Nina serre l'oreille, sans bouger. Garde la mer pour moi. Elle t'attend. Tu as proposé une autre heure. Elle a dit oui, pour plus tard. Amir laisse un siège vide, à dessein. [pause]</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -6635,7 +6635,7 @@
 enfant-f|Oui, plus tard.
 enfant-m|D'accord.
 narrateur|La vitre garde sa place, sans lui.
-narrateur|Nina serre l'oreille, toujours.
+narrateur|Nina serre l'oreille, sans bouger.
 enfant-f|Garde la mer pour moi.
 enfant-m|Elle t'attend.
 papa|Tu as proposé une autre heure.
@@ -11756,17 +11756,17 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>On regarde plus tard, alors ? Oui, plus tard. D'accord. La tablette garde sa place, sans lui. Nina serre l'oreille, toujours. Garde la mer pour moi. Elle t'attend. Tu as proposé une autre heure. Elle a dit oui, pour plus tard. Le pain attend, plié, pour deux.</t>
+          <t>On regarde plus tard, alors ? Oui, plus tard. D'accord. La tablette garde sa place, sans lui. Nina serre l'oreille, sans bouger. Garde la mer pour moi. Elle t'attend. Tu as proposé une autre heure. Elle a dit oui, pour plus tard. Le pain attend, plié, pour deux.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;On regarde &lt;emphasis level="moderate"&gt;plus tard&lt;/emphasis&gt;, alors ? Oui, plus tard. D'accord. La tablette garde sa place, sans lui. Nina serre l'oreille, toujours. Garde la mer pour moi. Elle t'attend. Tu as proposé une autre heure. Elle a dit oui, pour plus tard. Le pain attend, plié, pour deux.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;On regarde &lt;emphasis level="moderate"&gt;plus tard&lt;/emphasis&gt;, alors ? Oui, plus tard. D'accord. La tablette garde sa place, sans lui. Nina serre l'oreille, sans bouger. Garde la mer pour moi. Elle t'attend. Tu as proposé une autre heure. Elle a dit oui, pour plus tard. Le pain attend, plié, pour deux.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>On regarde &lt;emphasis&gt;plus tard&lt;/emphasis&gt;, alors ? Oui, plus tard. D'accord. La tablette garde sa place, sans lui. Nina serre l'oreille, toujours. Garde la mer pour moi. Elle t'attend. Tu as proposé une autre heure. Elle a dit oui, pour plus tard. Le pain attend, plié, pour deux. [pause]</t>
+          <t>On regarde &lt;emphasis&gt;plus tard&lt;/emphasis&gt;, alors ? Oui, plus tard. D'accord. La tablette garde sa place, sans lui. Nina serre l'oreille, sans bouger. Garde la mer pour moi. Elle t'attend. Tu as proposé une autre heure. Elle a dit oui, pour plus tard. Le pain attend, plié, pour deux. [pause]</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
@@ -11904,7 +11904,7 @@
 enfant-f|Oui, plus tard.
 enfant-m|D'accord.
 narrateur|La tablette garde sa place, sans lui.
-narrateur|Nina serre l'oreille, toujours.
+narrateur|Nina serre l'oreille, sans bouger.
 enfant-f|Garde la mer pour moi.
 enfant-m|Elle t'attend.
 papa|Tu as proposé une autre heure.
@@ -17022,17 +17022,17 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>On regarde plus tard, alors ? Oui, plus tard. D'accord. La porte garde sa place, sans lui. Nina serre l'oreille, toujours. Garde la mer pour moi. Elle t'attend. Tu as proposé une autre heure. Elle a dit oui, pour plus tard. Amir garde un bout de barre, libre.</t>
+          <t>On regarde plus tard, alors ? Oui, plus tard. D'accord. La porte garde sa place, sans lui. Nina serre l'oreille, sans bouger. Garde la mer pour moi. Elle t'attend. Tu as proposé une autre heure. Elle a dit oui, pour plus tard. Amir garde un bout de barre, libre.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;On regarde &lt;emphasis level="moderate"&gt;plus tard&lt;/emphasis&gt;, alors ? Oui, plus tard. D'accord. La porte garde sa place, sans lui. Nina serre l'oreille, toujours. Garde la mer pour moi. Elle t'attend. Tu as proposé une autre heure. Elle a dit oui, pour plus tard. Amir garde un bout de barre, libre.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;On regarde &lt;emphasis level="moderate"&gt;plus tard&lt;/emphasis&gt;, alors ? Oui, plus tard. D'accord. La porte garde sa place, sans lui. Nina serre l'oreille, sans bouger. Garde la mer pour moi. Elle t'attend. Tu as proposé une autre heure. Elle a dit oui, pour plus tard. Amir garde un bout de barre, libre.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>On regarde &lt;emphasis&gt;plus tard&lt;/emphasis&gt;, alors ? Oui, plus tard. D'accord. La porte garde sa place, sans lui. Nina serre l'oreille, toujours. Garde la mer pour moi. Elle t'attend. Tu as proposé une autre heure. Elle a dit oui, pour plus tard. Amir garde un bout de barre, libre. [pause]</t>
+          <t>On regarde &lt;emphasis&gt;plus tard&lt;/emphasis&gt;, alors ? Oui, plus tard. D'accord. La porte garde sa place, sans lui. Nina serre l'oreille, sans bouger. Garde la mer pour moi. Elle t'attend. Tu as proposé une autre heure. Elle a dit oui, pour plus tard. Amir garde un bout de barre, libre. [pause]</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr"/>
@@ -17170,7 +17170,7 @@
 enfant-f|Oui, plus tard.
 enfant-m|D'accord.
 narrateur|La porte garde sa place, sans lui.
-narrateur|Nina serre l'oreille, toujours.
+narrateur|Nina serre l'oreille, sans bouger.
 enfant-f|Garde la mer pour moi.
 enfant-m|Elle t'attend.
 papa|Tu as proposé une autre heure.
@@ -17389,7 +17389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -17446,6 +17446,13 @@
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
